--- a/artfynd/A 24000-2026 artfynd.xlsx
+++ b/artfynd/A 24000-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ5"/>
+  <dimension ref="A1:AZ16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -680,60 +680,48 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>72475294</v>
+        <v>136457028</v>
       </c>
       <c r="B2" t="n">
-        <v>56925</v>
+        <v>92113</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100045</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Sångsvan</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Cygnus cygnus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>rastande</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr"/>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Ersträskbäcken, Koler, Nb</t>
+          <t>Nygård, Nb</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>754651</v>
+        <v>754363</v>
       </c>
       <c r="R2" t="n">
-        <v>7272886</v>
+        <v>7271790</v>
       </c>
       <c r="S2" t="n">
-        <v>50</v>
+        <v>11</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -757,17 +745,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2018-07-29</t>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>16:09</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2018-07-29</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>2 adulta och 2 1k.</t>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>16:09</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,27 +775,27 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Björn Goldkuhl</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Björn Goldkuhl</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/72475294</t>
+          <t>https://artportalen.se/Sighting/136457028</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>77427419</v>
+        <v>136457037</v>
       </c>
       <c r="B3" t="n">
-        <v>57094</v>
+        <v>93449</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -810,53 +803,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>102931</v>
+        <v>5966</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Bläsand</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Mareca penelope</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>i par</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>obs i häcktid, lämplig biotop</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Ersträskbäcken, Koler, Nb</t>
+          <t>Nygård, Nb</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>754651</v>
+        <v>754451</v>
       </c>
       <c r="R3" t="n">
-        <v>7272886</v>
+        <v>7272864</v>
       </c>
       <c r="S3" t="n">
-        <v>50</v>
+        <v>15</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -880,12 +857,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2019-04-30</t>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>16:56</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2019-04-30</t>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>16:56</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -900,27 +887,27 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Björn Goldkuhl</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Björn Goldkuhl</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/77427419</t>
+          <t>https://artportalen.se/Sighting/136457037</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>53258400</v>
+        <v>136457040</v>
       </c>
       <c r="B4" t="n">
-        <v>57105</v>
+        <v>80095</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -928,52 +915,37 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>102932</v>
+        <v>6453</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kricka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Anas crecca</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>rastande</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Ersträskbäcken, Koler, Nb</t>
+          <t>Nygård, Nb</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>754651</v>
+        <v>754473</v>
       </c>
       <c r="R4" t="n">
-        <v>7272886</v>
+        <v>7272718</v>
       </c>
       <c r="S4" t="n">
-        <v>50</v>
+        <v>15</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -997,12 +969,22 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2015-05-06</t>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>17:15</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2015-05-06</t>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>17:15</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1017,54 +999,54 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Björn Goldkuhl</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Björn Goldkuhl</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/53258400</t>
+          <t>https://artportalen.se/Sighting/136457040</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>58751887</v>
+        <v>72475294</v>
       </c>
       <c r="B5" t="n">
-        <v>58393</v>
+        <v>56925</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>102999</v>
+        <v>100045</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Björktrast</t>
+          <t>Sångsvan</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Turdus pilaris</t>
+          <t>Cygnus cygnus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
@@ -1074,6 +1056,7 @@
           <t>rastande</t>
         </is>
       </c>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Ersträskbäcken, Koler, Nb</t>
@@ -1110,12 +1093,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2016-04-22</t>
+          <t>2018-07-29</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2016-04-22</t>
+          <t>2018-07-29</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>2 adulta och 2 1k.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1141,7 +1129,1326 @@
       <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="inlineStr">
         <is>
+          <t>https://artportalen.se/Sighting/72475294</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>136457029</v>
+      </c>
+      <c r="B6" t="n">
+        <v>58008</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Nygård, Nb</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>754324</v>
+      </c>
+      <c r="R6" t="n">
+        <v>7271783</v>
+      </c>
+      <c r="S6" t="n">
+        <v>5</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Piteå</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Piteå socken</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>16:13</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>16:13</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136457029</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>136457030</v>
+      </c>
+      <c r="B7" t="n">
+        <v>58008</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Nygård, Nb</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>754326</v>
+      </c>
+      <c r="R7" t="n">
+        <v>7271866</v>
+      </c>
+      <c r="S7" t="n">
+        <v>5</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Piteå</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Piteå socken</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>16:16</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>16:16</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136457030</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>136457031</v>
+      </c>
+      <c r="B8" t="n">
+        <v>58008</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Nygård, Nb</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>754332</v>
+      </c>
+      <c r="R8" t="n">
+        <v>7271879</v>
+      </c>
+      <c r="S8" t="n">
+        <v>21</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Piteå</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Piteå socken</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>16:17</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>16:17</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136457031</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>136457032</v>
+      </c>
+      <c r="B9" t="n">
+        <v>58008</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Nygård, Nb</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>754328</v>
+      </c>
+      <c r="R9" t="n">
+        <v>7271959</v>
+      </c>
+      <c r="S9" t="n">
+        <v>11</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Piteå</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Piteå socken</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>16:20</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>16:20</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136457032</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>136457034</v>
+      </c>
+      <c r="B10" t="n">
+        <v>58008</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Nygård, Nb</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>754313</v>
+      </c>
+      <c r="R10" t="n">
+        <v>7272205</v>
+      </c>
+      <c r="S10" t="n">
+        <v>22</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Piteå</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Piteå socken</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>16:29</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>16:29</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136457034</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>136457035</v>
+      </c>
+      <c r="B11" t="n">
+        <v>58008</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Nygård, Nb</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>754308</v>
+      </c>
+      <c r="R11" t="n">
+        <v>7272263</v>
+      </c>
+      <c r="S11" t="n">
+        <v>5</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Piteå</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Piteå socken</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>16:31</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>16:31</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136457035</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>136457041</v>
+      </c>
+      <c r="B12" t="n">
+        <v>58008</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Nygård, Nb</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>754386</v>
+      </c>
+      <c r="R12" t="n">
+        <v>7271761</v>
+      </c>
+      <c r="S12" t="n">
+        <v>14</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Piteå</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Piteå socken</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>17:56</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>17:56</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136457041</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>77427419</v>
+      </c>
+      <c r="B13" t="n">
+        <v>57094</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>102931</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Bläsand</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Mareca penelope</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Ersträskbäcken, Koler, Nb</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>754651</v>
+      </c>
+      <c r="R13" t="n">
+        <v>7272886</v>
+      </c>
+      <c r="S13" t="n">
+        <v>50</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Piteå</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Piteå socken</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2019-04-30</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2019-04-30</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Björn Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Björn Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/77427419</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>53258400</v>
+      </c>
+      <c r="B14" t="n">
+        <v>57105</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>102932</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Kricka</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Anas crecca</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>rastande</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Ersträskbäcken, Koler, Nb</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>754651</v>
+      </c>
+      <c r="R14" t="n">
+        <v>7272886</v>
+      </c>
+      <c r="S14" t="n">
+        <v>50</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Piteå</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Piteå socken</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2015-05-06</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2015-05-06</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Björn Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Björn Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/53258400</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>58751887</v>
+      </c>
+      <c r="B15" t="n">
+        <v>58393</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>102999</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Björktrast</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Turdus pilaris</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>rastande</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Ersträskbäcken, Koler, Nb</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>754651</v>
+      </c>
+      <c r="R15" t="n">
+        <v>7272886</v>
+      </c>
+      <c r="S15" t="n">
+        <v>50</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Piteå</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Piteå socken</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2016-04-22</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2016-04-22</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Björn Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Björn Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
           <t>https://artportalen.se/Sighting/58751887</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>136457039</v>
+      </c>
+      <c r="B16" t="n">
+        <v>58169</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Nygård, Nb</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>754405</v>
+      </c>
+      <c r="R16" t="n">
+        <v>7272927</v>
+      </c>
+      <c r="S16" t="n">
+        <v>15</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Piteå</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Piteå socken</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>17:03</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>17:03</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136457039</t>
         </is>
       </c>
     </row>
@@ -1151,6 +2458,17 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 24000-2026 artfynd.xlsx
+++ b/artfynd/A 24000-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136457028</v>
       </c>
       <c r="B2" t="n">
-        <v>92113</v>
+        <v>92115</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136457037</v>
       </c>
       <c r="B3" t="n">
-        <v>93449</v>
+        <v>93451</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136457040</v>
       </c>
       <c r="B4" t="n">
-        <v>80095</v>
+        <v>80099</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 24000-2026 artfynd.xlsx
+++ b/artfynd/A 24000-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136457028</v>
       </c>
       <c r="B2" t="n">
-        <v>92115</v>
+        <v>92117</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136457037</v>
       </c>
       <c r="B3" t="n">
-        <v>93451</v>
+        <v>93453</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136457040</v>
       </c>
       <c r="B4" t="n">
-        <v>80099</v>
+        <v>80101</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 24000-2026 artfynd.xlsx
+++ b/artfynd/A 24000-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136457028</v>
       </c>
       <c r="B2" t="n">
-        <v>92117</v>
+        <v>92118</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136457037</v>
       </c>
       <c r="B3" t="n">
-        <v>93453</v>
+        <v>93454</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136457040</v>
       </c>
       <c r="B4" t="n">
-        <v>80101</v>
+        <v>80102</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 24000-2026 artfynd.xlsx
+++ b/artfynd/A 24000-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136457028</v>
       </c>
       <c r="B2" t="n">
-        <v>92118</v>
+        <v>92124</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136457037</v>
       </c>
       <c r="B3" t="n">
-        <v>93454</v>
+        <v>93460</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 24000-2026 artfynd.xlsx
+++ b/artfynd/A 24000-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136457028</v>
       </c>
       <c r="B2" t="n">
-        <v>92124</v>
+        <v>92128</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136457037</v>
       </c>
       <c r="B3" t="n">
-        <v>93460</v>
+        <v>93464</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136457040</v>
       </c>
       <c r="B4" t="n">
-        <v>80102</v>
+        <v>80104</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 24000-2026 artfynd.xlsx
+++ b/artfynd/A 24000-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136457028</v>
       </c>
       <c r="B2" t="n">
-        <v>92128</v>
+        <v>92130</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136457037</v>
       </c>
       <c r="B3" t="n">
-        <v>93464</v>
+        <v>93466</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136457040</v>
       </c>
       <c r="B4" t="n">
-        <v>80104</v>
+        <v>80107</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 24000-2026 artfynd.xlsx
+++ b/artfynd/A 24000-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136457028</v>
       </c>
       <c r="B2" t="n">
-        <v>92130</v>
+        <v>92143</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136457037</v>
       </c>
       <c r="B3" t="n">
-        <v>93466</v>
+        <v>93479</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136457040</v>
       </c>
       <c r="B4" t="n">
-        <v>80107</v>
+        <v>80120</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1138,7 +1138,7 @@
         <v>136457029</v>
       </c>
       <c r="B6" t="n">
-        <v>58008</v>
+        <v>58021</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
         <v>136457030</v>
       </c>
       <c r="B7" t="n">
-        <v>58008</v>
+        <v>58021</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1382,7 +1382,7 @@
         <v>136457031</v>
       </c>
       <c r="B8" t="n">
-        <v>58008</v>
+        <v>58021</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1504,7 +1504,7 @@
         <v>136457032</v>
       </c>
       <c r="B9" t="n">
-        <v>58008</v>
+        <v>58021</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1626,7 +1626,7 @@
         <v>136457034</v>
       </c>
       <c r="B10" t="n">
-        <v>58008</v>
+        <v>58021</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1748,7 +1748,7 @@
         <v>136457035</v>
       </c>
       <c r="B11" t="n">
-        <v>58008</v>
+        <v>58021</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1870,7 +1870,7 @@
         <v>136457041</v>
       </c>
       <c r="B12" t="n">
-        <v>58008</v>
+        <v>58021</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2340,7 +2340,7 @@
         <v>136457039</v>
       </c>
       <c r="B16" t="n">
-        <v>58169</v>
+        <v>58182</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/artfynd/A 24000-2026 artfynd.xlsx
+++ b/artfynd/A 24000-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136457028</v>
       </c>
       <c r="B2" t="n">
-        <v>92143</v>
+        <v>92145</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136457037</v>
       </c>
       <c r="B3" t="n">
-        <v>93479</v>
+        <v>93480</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136457040</v>
       </c>
       <c r="B4" t="n">
-        <v>80120</v>
+        <v>80122</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1138,7 +1138,7 @@
         <v>136457029</v>
       </c>
       <c r="B6" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
         <v>136457030</v>
       </c>
       <c r="B7" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1382,7 +1382,7 @@
         <v>136457031</v>
       </c>
       <c r="B8" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1504,7 +1504,7 @@
         <v>136457032</v>
       </c>
       <c r="B9" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1626,7 +1626,7 @@
         <v>136457034</v>
       </c>
       <c r="B10" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1748,7 +1748,7 @@
         <v>136457035</v>
       </c>
       <c r="B11" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1870,7 +1870,7 @@
         <v>136457041</v>
       </c>
       <c r="B12" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2340,7 +2340,7 @@
         <v>136457039</v>
       </c>
       <c r="B16" t="n">
-        <v>58182</v>
+        <v>58184</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/artfynd/A 24000-2026 artfynd.xlsx
+++ b/artfynd/A 24000-2026 artfynd.xlsx
@@ -1164,11 +1164,7 @@
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="M6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Nygård, Nb</t>
@@ -1286,11 +1282,7 @@
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="M7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Nygård, Nb</t>
@@ -1408,11 +1400,7 @@
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="M8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Nygård, Nb</t>
@@ -1530,11 +1518,7 @@
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="M9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Nygård, Nb</t>
@@ -1652,11 +1636,7 @@
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="M10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Nygård, Nb</t>
@@ -1774,11 +1754,7 @@
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="M11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Nygård, Nb</t>
@@ -1896,11 +1872,7 @@
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="M12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Nygård, Nb</t>
@@ -2366,11 +2338,7 @@
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+      <c r="M16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Nygård, Nb</t>

--- a/artfynd/A 24000-2026 artfynd.xlsx
+++ b/artfynd/A 24000-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136457028</v>
       </c>
       <c r="B2" t="n">
-        <v>92145</v>
+        <v>92148</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136457037</v>
       </c>
       <c r="B3" t="n">
-        <v>93480</v>
+        <v>93483</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 24000-2026 artfynd.xlsx
+++ b/artfynd/A 24000-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136457028</v>
       </c>
       <c r="B2" t="n">
-        <v>92148</v>
+        <v>92158</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136457037</v>
       </c>
       <c r="B3" t="n">
-        <v>93483</v>
+        <v>93493</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136457040</v>
       </c>
       <c r="B4" t="n">
-        <v>80122</v>
+        <v>80132</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1138,7 +1138,7 @@
         <v>136457029</v>
       </c>
       <c r="B6" t="n">
-        <v>58023</v>
+        <v>58033</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1256,7 +1256,7 @@
         <v>136457030</v>
       </c>
       <c r="B7" t="n">
-        <v>58023</v>
+        <v>58033</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1374,7 +1374,7 @@
         <v>136457031</v>
       </c>
       <c r="B8" t="n">
-        <v>58023</v>
+        <v>58033</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1492,7 +1492,7 @@
         <v>136457032</v>
       </c>
       <c r="B9" t="n">
-        <v>58023</v>
+        <v>58033</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1610,7 +1610,7 @@
         <v>136457034</v>
       </c>
       <c r="B10" t="n">
-        <v>58023</v>
+        <v>58033</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1728,7 +1728,7 @@
         <v>136457035</v>
       </c>
       <c r="B11" t="n">
-        <v>58023</v>
+        <v>58033</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1846,7 +1846,7 @@
         <v>136457041</v>
       </c>
       <c r="B12" t="n">
-        <v>58023</v>
+        <v>58033</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2312,7 +2312,7 @@
         <v>136457039</v>
       </c>
       <c r="B16" t="n">
-        <v>58184</v>
+        <v>58194</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/artfynd/A 24000-2026 artfynd.xlsx
+++ b/artfynd/A 24000-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136457028</v>
       </c>
       <c r="B2" t="n">
-        <v>92158</v>
+        <v>92159</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136457037</v>
       </c>
       <c r="B3" t="n">
-        <v>93493</v>
+        <v>93494</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 24000-2026 artfynd.xlsx
+++ b/artfynd/A 24000-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136457028</v>
       </c>
       <c r="B2" t="n">
-        <v>92159</v>
+        <v>92162</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136457037</v>
       </c>
       <c r="B3" t="n">
-        <v>93494</v>
+        <v>93499</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136457040</v>
       </c>
       <c r="B4" t="n">
-        <v>80132</v>
+        <v>80135</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1138,7 +1138,7 @@
         <v>136457029</v>
       </c>
       <c r="B6" t="n">
-        <v>58033</v>
+        <v>58034</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1256,7 +1256,7 @@
         <v>136457030</v>
       </c>
       <c r="B7" t="n">
-        <v>58033</v>
+        <v>58034</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1374,7 +1374,7 @@
         <v>136457031</v>
       </c>
       <c r="B8" t="n">
-        <v>58033</v>
+        <v>58034</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1492,7 +1492,7 @@
         <v>136457032</v>
       </c>
       <c r="B9" t="n">
-        <v>58033</v>
+        <v>58034</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1610,7 +1610,7 @@
         <v>136457034</v>
       </c>
       <c r="B10" t="n">
-        <v>58033</v>
+        <v>58034</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1728,7 +1728,7 @@
         <v>136457035</v>
       </c>
       <c r="B11" t="n">
-        <v>58033</v>
+        <v>58034</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1846,7 +1846,7 @@
         <v>136457041</v>
       </c>
       <c r="B12" t="n">
-        <v>58033</v>
+        <v>58034</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2312,7 +2312,7 @@
         <v>136457039</v>
       </c>
       <c r="B16" t="n">
-        <v>58194</v>
+        <v>58195</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/artfynd/A 24000-2026 artfynd.xlsx
+++ b/artfynd/A 24000-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136457028</v>
       </c>
       <c r="B2" t="n">
-        <v>92162</v>
+        <v>92164</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136457037</v>
       </c>
       <c r="B3" t="n">
-        <v>93499</v>
+        <v>93501</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 24000-2026 artfynd.xlsx
+++ b/artfynd/A 24000-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136457028</v>
       </c>
       <c r="B2" t="n">
-        <v>92164</v>
+        <v>92169</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136457037</v>
       </c>
       <c r="B3" t="n">
-        <v>93501</v>
+        <v>93507</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136457040</v>
       </c>
       <c r="B4" t="n">
-        <v>80135</v>
+        <v>80140</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1138,7 +1138,7 @@
         <v>136457029</v>
       </c>
       <c r="B6" t="n">
-        <v>58034</v>
+        <v>58035</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1256,7 +1256,7 @@
         <v>136457030</v>
       </c>
       <c r="B7" t="n">
-        <v>58034</v>
+        <v>58035</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1374,7 +1374,7 @@
         <v>136457031</v>
       </c>
       <c r="B8" t="n">
-        <v>58034</v>
+        <v>58035</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1492,7 +1492,7 @@
         <v>136457032</v>
       </c>
       <c r="B9" t="n">
-        <v>58034</v>
+        <v>58035</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1610,7 +1610,7 @@
         <v>136457034</v>
       </c>
       <c r="B10" t="n">
-        <v>58034</v>
+        <v>58035</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1728,7 +1728,7 @@
         <v>136457035</v>
       </c>
       <c r="B11" t="n">
-        <v>58034</v>
+        <v>58035</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1846,7 +1846,7 @@
         <v>136457041</v>
       </c>
       <c r="B12" t="n">
-        <v>58034</v>
+        <v>58035</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2312,7 +2312,7 @@
         <v>136457039</v>
       </c>
       <c r="B16" t="n">
-        <v>58195</v>
+        <v>58196</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/artfynd/A 24000-2026 artfynd.xlsx
+++ b/artfynd/A 24000-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136457028</v>
       </c>
       <c r="B2" t="n">
-        <v>92169</v>
+        <v>92181</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136457037</v>
       </c>
       <c r="B3" t="n">
-        <v>93507</v>
+        <v>93519</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136457040</v>
       </c>
       <c r="B4" t="n">
-        <v>80140</v>
+        <v>80151</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 24000-2026 artfynd.xlsx
+++ b/artfynd/A 24000-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136457028</v>
       </c>
       <c r="B2" t="n">
-        <v>92181</v>
+        <v>92182</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136457037</v>
       </c>
       <c r="B3" t="n">
-        <v>93519</v>
+        <v>93520</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136457040</v>
       </c>
       <c r="B4" t="n">
-        <v>80151</v>
+        <v>80152</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 24000-2026 artfynd.xlsx
+++ b/artfynd/A 24000-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136457028</v>
       </c>
       <c r="B2" t="n">
-        <v>92182</v>
+        <v>92185</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136457037</v>
       </c>
       <c r="B3" t="n">
-        <v>93520</v>
+        <v>93523</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136457040</v>
       </c>
       <c r="B4" t="n">
-        <v>80152</v>
+        <v>80154</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 24000-2026 artfynd.xlsx
+++ b/artfynd/A 24000-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136457028</v>
       </c>
       <c r="B2" t="n">
-        <v>92185</v>
+        <v>92186</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136457037</v>
       </c>
       <c r="B3" t="n">
-        <v>93523</v>
+        <v>93524</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136457040</v>
       </c>
       <c r="B4" t="n">
-        <v>80154</v>
+        <v>80155</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 24000-2026 artfynd.xlsx
+++ b/artfynd/A 24000-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136457028</v>
       </c>
       <c r="B2" t="n">
-        <v>92186</v>
+        <v>92189</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136457037</v>
       </c>
       <c r="B3" t="n">
-        <v>93524</v>
+        <v>93527</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136457040</v>
       </c>
       <c r="B4" t="n">
-        <v>80155</v>
+        <v>80158</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1138,7 +1138,7 @@
         <v>136457029</v>
       </c>
       <c r="B6" t="n">
-        <v>58035</v>
+        <v>58038</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1256,7 +1256,7 @@
         <v>136457030</v>
       </c>
       <c r="B7" t="n">
-        <v>58035</v>
+        <v>58038</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1374,7 +1374,7 @@
         <v>136457031</v>
       </c>
       <c r="B8" t="n">
-        <v>58035</v>
+        <v>58038</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1492,7 +1492,7 @@
         <v>136457032</v>
       </c>
       <c r="B9" t="n">
-        <v>58035</v>
+        <v>58038</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1610,7 +1610,7 @@
         <v>136457034</v>
       </c>
       <c r="B10" t="n">
-        <v>58035</v>
+        <v>58038</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1728,7 +1728,7 @@
         <v>136457035</v>
       </c>
       <c r="B11" t="n">
-        <v>58035</v>
+        <v>58038</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1846,7 +1846,7 @@
         <v>136457041</v>
       </c>
       <c r="B12" t="n">
-        <v>58035</v>
+        <v>58038</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2312,7 +2312,7 @@
         <v>136457039</v>
       </c>
       <c r="B16" t="n">
-        <v>58196</v>
+        <v>58199</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
